--- a/public/demo/prismlaunch-supplier-demo.xlsx
+++ b/public/demo/prismlaunch-supplier-demo.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:S9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,6 +442,21 @@
       <c r="N1" t="str">
         <v>packageHeightCm</v>
       </c>
+      <c r="O1" t="str">
+        <v>reportNo</v>
+      </c>
+      <c r="P1" t="str">
+        <v>reportResult</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>reportValidUntil</v>
+      </c>
+      <c r="R1" t="str">
+        <v>reportCapacityMl</v>
+      </c>
+      <c r="S1" t="str">
+        <v>reportMaterial</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -486,6 +501,15 @@
       <c r="N2" t="str">
         <v>25</v>
       </c>
+      <c r="O2" t="str">
+        <v>QC-2026-1001</v>
+      </c>
+      <c r="P2" t="str">
+        <v>pass</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>2027-06-30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -498,7 +522,7 @@
         <v>Home &amp; Kitchen</v>
       </c>
       <c r="D3" t="str">
-        <v>Black</v>
+        <v>Gray</v>
       </c>
       <c r="E3" t="str">
         <v>500</v>
@@ -526,6 +550,15 @@
       </c>
       <c r="N3" t="str">
         <v>25</v>
+      </c>
+      <c r="O3" t="str">
+        <v>QC-2026-1001</v>
+      </c>
+      <c r="P3" t="str">
+        <v>pass</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>2027-06-30</v>
       </c>
     </row>
     <row r="4">
@@ -571,6 +604,15 @@
       <c r="N4" t="str">
         <v>26</v>
       </c>
+      <c r="O4" t="str">
+        <v>QC-2026-1001</v>
+      </c>
+      <c r="P4" t="str">
+        <v>pass</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>2027-06-30</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -615,6 +657,15 @@
       <c r="N5" t="str">
         <v>29</v>
       </c>
+      <c r="O5" t="str">
+        <v>QC-2026-1001</v>
+      </c>
+      <c r="P5" t="str">
+        <v>pass</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>2027-06-30</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -659,6 +710,15 @@
       <c r="N6" t="str">
         <v>25</v>
       </c>
+      <c r="O6" t="str">
+        <v>QC-2026-1001</v>
+      </c>
+      <c r="P6" t="str">
+        <v>pass</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>2027-06-30</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -703,6 +763,15 @@
       <c r="N7" t="str">
         <v>25</v>
       </c>
+      <c r="O7" t="str">
+        <v>QC-2026-1001</v>
+      </c>
+      <c r="P7" t="str">
+        <v>pass</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>2027-06-30</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -747,6 +816,15 @@
       <c r="N8" t="str">
         <v>25</v>
       </c>
+      <c r="O8" t="str">
+        <v>QC-2026-1001</v>
+      </c>
+      <c r="P8" t="str">
+        <v>pass</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>2027-06-30</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -791,10 +869,19 @@
       <c r="N9" t="str">
         <v>25</v>
       </c>
+      <c r="O9" t="str">
+        <v>QC-2026-1001</v>
+      </c>
+      <c r="P9" t="str">
+        <v>pass</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>2027-06-30</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/demo/prismlaunch-supplier-demo.xlsx
+++ b/public/demo/prismlaunch-supplier-demo.xlsx
@@ -501,15 +501,6 @@
       <c r="N2" t="str">
         <v>25</v>
       </c>
-      <c r="O2" t="str">
-        <v>QC-2026-1001</v>
-      </c>
-      <c r="P2" t="str">
-        <v>pass</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>2027-06-30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -551,15 +542,6 @@
       <c r="N3" t="str">
         <v>25</v>
       </c>
-      <c r="O3" t="str">
-        <v>QC-2026-1001</v>
-      </c>
-      <c r="P3" t="str">
-        <v>pass</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>2027-06-30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -604,15 +586,6 @@
       <c r="N4" t="str">
         <v>26</v>
       </c>
-      <c r="O4" t="str">
-        <v>QC-2026-1001</v>
-      </c>
-      <c r="P4" t="str">
-        <v>pass</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>2027-06-30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -657,15 +630,6 @@
       <c r="N5" t="str">
         <v>29</v>
       </c>
-      <c r="O5" t="str">
-        <v>QC-2026-1001</v>
-      </c>
-      <c r="P5" t="str">
-        <v>pass</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>2027-06-30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -710,15 +674,6 @@
       <c r="N6" t="str">
         <v>25</v>
       </c>
-      <c r="O6" t="str">
-        <v>QC-2026-1001</v>
-      </c>
-      <c r="P6" t="str">
-        <v>pass</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>2027-06-30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -763,15 +718,6 @@
       <c r="N7" t="str">
         <v>25</v>
       </c>
-      <c r="O7" t="str">
-        <v>QC-2026-1001</v>
-      </c>
-      <c r="P7" t="str">
-        <v>pass</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>2027-06-30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -816,15 +762,6 @@
       <c r="N8" t="str">
         <v>25</v>
       </c>
-      <c r="O8" t="str">
-        <v>QC-2026-1001</v>
-      </c>
-      <c r="P8" t="str">
-        <v>pass</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>2027-06-30</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -868,15 +805,6 @@
       </c>
       <c r="N9" t="str">
         <v>25</v>
-      </c>
-      <c r="O9" t="str">
-        <v>QC-2026-1001</v>
-      </c>
-      <c r="P9" t="str">
-        <v>pass</v>
-      </c>
-      <c r="Q9" t="str">
-        <v>2027-06-30</v>
       </c>
     </row>
   </sheetData>
